--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.18879045718127</v>
+        <v>10.10567844929196</v>
       </c>
       <c r="D2" t="n">
-        <v>61.59375187906246</v>
+        <v>10.00898468034765</v>
       </c>
       <c r="E2" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F2" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.79016418581609</v>
+        <v>10.20340168019511</v>
       </c>
       <c r="D3" t="n">
-        <v>62.15092869787325</v>
+        <v>10.0995259134044</v>
       </c>
       <c r="E3" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F3" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>66.87658946521418</v>
+        <v>10.8674457880973</v>
       </c>
       <c r="D4" t="n">
-        <v>66.20851775775748</v>
+        <v>10.75888413563559</v>
       </c>
       <c r="E4" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F4" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.55326470572337</v>
+        <v>7.402405514680048</v>
       </c>
       <c r="D5" t="n">
-        <v>44.89661421764078</v>
+        <v>7.295699810366627</v>
       </c>
       <c r="E5" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F5" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.11651284873032</v>
+        <v>8.631433337918677</v>
       </c>
       <c r="D6" t="n">
-        <v>52.45053341980598</v>
+        <v>8.523211680718472</v>
       </c>
       <c r="E6" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F6" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.36475191496636</v>
+        <v>6.071772186182034</v>
       </c>
       <c r="D7" t="n">
-        <v>37.09165137834423</v>
+        <v>6.027393348980937</v>
       </c>
       <c r="E7" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F7" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.50993505974846</v>
+        <v>4.795364447209125</v>
       </c>
       <c r="D8" t="n">
-        <v>29.03411261970183</v>
+        <v>4.718043300701548</v>
       </c>
       <c r="E8" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F8" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.19859979993067</v>
+        <v>5.557272467488734</v>
       </c>
       <c r="D9" t="n">
-        <v>34.04620438125036</v>
+        <v>5.532508211953183</v>
       </c>
       <c r="E9" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F9" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>58.52907569346085</v>
+        <v>9.510974800187388</v>
       </c>
       <c r="D10" t="n">
-        <v>57.92770640163468</v>
+        <v>9.413252290265635</v>
       </c>
       <c r="E10" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F10" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>20.38492178217307</v>
+        <v>3.312549789603124</v>
       </c>
       <c r="D11" t="n">
-        <v>20.13775121281119</v>
+        <v>3.272384572081818</v>
       </c>
       <c r="E11" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F11" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>58.7479326493953</v>
+        <v>9.546539055526736</v>
       </c>
       <c r="D12" t="n">
-        <v>58.22398032839781</v>
+        <v>9.461396803364645</v>
       </c>
       <c r="E12" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F12" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>47.48406032978761</v>
+        <v>7.716159803590487</v>
       </c>
       <c r="D13" t="n">
-        <v>46.94225851461636</v>
+        <v>7.628117008625159</v>
       </c>
       <c r="E13" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F13" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.18758756707246</v>
+        <v>7.017982979649275</v>
       </c>
       <c r="D14" t="n">
-        <v>43.46471614343555</v>
+        <v>7.063016373308278</v>
       </c>
       <c r="E14" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F14" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>48.80326018102127</v>
+        <v>7.930529779415957</v>
       </c>
       <c r="D15" t="n">
-        <v>49.21430914819703</v>
+        <v>7.997325236582018</v>
       </c>
       <c r="E15" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F15" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>51.8691107913443</v>
+        <v>8.428730503593449</v>
       </c>
       <c r="D16" t="n">
-        <v>51.66764949769878</v>
+        <v>8.395993043376052</v>
       </c>
       <c r="E16" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F16" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>36.13015411527439</v>
+        <v>5.871150043732089</v>
       </c>
       <c r="D17" t="n">
-        <v>36.12981137231661</v>
+        <v>5.871094348001449</v>
       </c>
       <c r="E17" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F17" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>27.03443144081332</v>
+        <v>4.393095109132165</v>
       </c>
       <c r="D18" t="n">
-        <v>27.3179480401176</v>
+        <v>4.439166556519111</v>
       </c>
       <c r="E18" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F18" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>59.49397428535819</v>
+        <v>9.667770821370706</v>
       </c>
       <c r="D19" t="n">
-        <v>60.05882083947674</v>
+        <v>9.759558386414971</v>
       </c>
       <c r="E19" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F19" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>42.04218439939151</v>
+        <v>6.831854964901121</v>
       </c>
       <c r="D20" t="n">
-        <v>42.16431942538482</v>
+        <v>6.851701906625033</v>
       </c>
       <c r="E20" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F20" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>56.7870423385616</v>
+        <v>9.227894380016259</v>
       </c>
       <c r="D21" t="n">
-        <v>57.42974718143363</v>
+        <v>9.332333916982964</v>
       </c>
       <c r="E21" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F21" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>68.75849654856502</v>
+        <v>11.17325568914182</v>
       </c>
       <c r="D22" t="n">
-        <v>69.41460193659637</v>
+        <v>11.27987281469691</v>
       </c>
       <c r="E22" t="n">
-        <v>13.34137783612049</v>
+        <v>2.16797389836958</v>
       </c>
       <c r="F22" t="n">
-        <v>13.32926564629674</v>
+        <v>2.16600566752322</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
